--- a/Face Advance Monthly orders/frontend/public/templates/cod-template.xlsx
+++ b/Face Advance Monthly orders/frontend/public/templates/cod-template.xlsx
@@ -484,6 +484,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="เลือกได้เฉพาะ ขนส่ง / ระบบ / ทำเคลม" promptTitle="ได้รับจาก" prompt="เลือก: ขนส่ง / ระบบ / ทำเคลม" type="list">
+      <formula1>"ขนส่ง,ระบบ,ทำเคลม"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -592,25 +597,22 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="n"/>
-    </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>ค่า "ได้รับจาก" ที่ใช้ได้: ขนส่ง · ระบบ · ทำเคลม (นอกเหนือจากนี้ระบบจะไม่รับ)</t>
+          <t>ค่า "ได้รับจาก" ที่ใช้ได้: ขนส่ง · ระบบ · ทำเคลม (ในชีตแรกมี dropdown ให้เลือก)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>"จำนวนเงิน" = ยอดที่รับจริง (ตัวเลขล้วน) · ถ้าไม่ตรงยอดออเดอร์ ระบบจะเตือนให้ตรวจสอบ</t>
+          <t>"จำนวนเงิน" = ยอดที่รับจริง (ตัวเลขล้วน) · ถ้าไม่ตรงยอดออเดอร์ ระบบจะเตือน</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>"หมายเลขพัสดุ" = เลขแทร็คส่งออก ต้องตรงกับในระบบ</t>
         </is>
